--- a/artfynd/S 4829-2022 artfynd.xlsx
+++ b/artfynd/S 4829-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY114"/>
+  <dimension ref="A1:AZ114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -771,6 +776,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96896026</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -869,6 +879,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96163697</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96895289</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1074,6 +1094,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99601671</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1181,6 +1206,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99601777</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1288,6 +1318,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99601665</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1395,6 +1430,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100603667</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1493,6 +1533,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96163645</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1600,6 +1645,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119474593</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1698,6 +1748,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96895469</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1796,6 +1851,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96895854</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1894,6 +1954,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96896616</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1992,6 +2057,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96895920</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2099,6 +2169,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99601478</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2197,6 +2272,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96896094</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2295,6 +2375,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96896206</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2393,6 +2478,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96896327</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2491,6 +2581,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96896871</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2598,6 +2693,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99601358</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2705,6 +2805,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99601392</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2812,6 +2917,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100603557</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2910,6 +3020,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96896331</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3017,6 +3132,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99601486</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3125,6 +3245,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99601647</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3224,6 +3349,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96895700</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3323,6 +3453,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96896411</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3426,6 +3561,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96895682</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3530,6 +3670,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96896753</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3634,6 +3779,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96896816</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3742,6 +3892,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99601632</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3850,6 +4005,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100603721</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3958,6 +4118,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100603906</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4057,6 +4222,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96895296</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4165,6 +4335,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100603291</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4273,6 +4448,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100603912</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4381,6 +4561,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100603307</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4480,6 +4665,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96895530</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4579,6 +4769,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96895703</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4678,6 +4873,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96895975</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4782,6 +4982,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96896222</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4881,6 +5086,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96896409</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4980,6 +5190,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96896607</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5079,6 +5294,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96896803</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5186,6 +5406,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99601482</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5294,6 +5519,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99602261</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5392,6 +5622,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96163457</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5493,6 +5728,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96163824</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5591,6 +5831,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96162161</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5689,6 +5934,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96159849</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5796,6 +6046,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99602964</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5894,6 +6149,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96163593</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5992,6 +6252,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96164589</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6090,6 +6355,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96160116</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6188,6 +6458,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96161019</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6286,6 +6561,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96161061</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6384,6 +6664,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96161157</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6482,6 +6767,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96161774</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6580,6 +6870,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96162072</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6678,6 +6973,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96162595</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6786,6 +7086,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96162605</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6884,6 +7189,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96162621</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6982,6 +7292,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96162639</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7080,6 +7395,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96162703</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7178,6 +7498,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96162817</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7276,6 +7601,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96163910</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7378,6 +7708,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97022801</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7476,6 +7811,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96160088</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7574,6 +7914,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96160637</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7672,6 +8017,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96159901</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7770,6 +8120,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96160810</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7868,6 +8223,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96159829</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7966,6 +8326,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96160706</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8064,6 +8429,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96160861</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8162,6 +8532,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96163111</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8260,6 +8635,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96163176</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8368,6 +8748,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96163205</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8466,6 +8851,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96163930</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8564,6 +8954,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96164080</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8662,6 +9057,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96164757</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8769,6 +9169,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99602972</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8876,6 +9281,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99603366</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8983,6 +9393,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99602968</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9088,6 +9503,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96160387</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9188,6 +9608,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96164621</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9304,6 +9729,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99602735</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9417,6 +9847,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100605797</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9516,6 +9951,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96163514</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9615,6 +10055,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96164199</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9723,6 +10168,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96163167</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9831,6 +10281,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96164180</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9939,6 +10394,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99603180</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10047,6 +10507,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100605154</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10155,6 +10620,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100606002</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10263,6 +10733,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100606092</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10362,6 +10837,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96160323</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10461,6 +10941,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96160818</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10560,6 +11045,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96164679</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10659,6 +11149,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96183993</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10758,6 +11253,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96160797</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10867,6 +11367,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96162166</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10966,6 +11471,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96160011</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11065,6 +11575,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96162891</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11173,6 +11688,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99602335</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11272,6 +11792,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96160777</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11371,6 +11896,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96163751</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11470,6 +12000,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96163959</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11569,6 +12104,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96164128</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11668,6 +12208,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96164212</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11766,6 +12311,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96160107</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11874,6 +12424,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96161100</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11972,6 +12527,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96163932</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12079,6 +12639,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99602981</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12177,8 +12742,128 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96163618</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>